--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124149516</v>
+        <v>124149514</v>
       </c>
       <c r="B2" t="n">
-        <v>56943</v>
+        <v>56703</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124169741</v>
+        <v>124149533</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -847,7 +847,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkberget, Skidtjärn  n, Hls</t>
+          <t>Kråkberget, Skidtjärn  NV, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149530</v>
+        <v>124149539</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,11 +963,6 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149539</v>
+        <v>124149519</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
+        <v>57187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,34 +1054,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124149519</v>
+        <v>124149516</v>
       </c>
       <c r="B6" t="n">
-        <v>57187</v>
+        <v>56943</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,37 +1178,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100063</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149514</v>
+        <v>124149536</v>
       </c>
       <c r="B7" t="n">
-        <v>56703</v>
+        <v>58033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,16 +1306,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102613</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149533</v>
+        <v>124149530</v>
       </c>
       <c r="B8" t="n">
-        <v>57920</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149536</v>
+        <v>124169741</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124149516</v>
+        <v>124149539</v>
       </c>
       <c r="B2" t="n">
-        <v>56965</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +715,6 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149536</v>
+        <v>124149526</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +806,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149530</v>
+        <v>124169741</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +930,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,7 +953,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1010,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149526</v>
+        <v>124149533</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,26 +1058,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1171,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124169741</v>
+        <v>124149536</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>58055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,20 +1178,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1258,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,7 +1263,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149539</v>
+        <v>124149519</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>57209</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,34 +1302,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149514</v>
+        <v>124149516</v>
       </c>
       <c r="B8" t="n">
-        <v>56725</v>
+        <v>56965</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149533</v>
+        <v>124149514</v>
       </c>
       <c r="B9" t="n">
-        <v>57942</v>
+        <v>56725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1662,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149519</v>
+        <v>124149530</v>
       </c>
       <c r="B10" t="n">
-        <v>57209</v>
+        <v>57883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,37 +1674,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100063</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149526</v>
+        <v>124149533</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,26 +810,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149533</v>
+        <v>124149526</v>
       </c>
       <c r="B5" t="n">
-        <v>57942</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,26 +1058,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149514</v>
+        <v>124149530</v>
       </c>
       <c r="B9" t="n">
-        <v>56725</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149530</v>
+        <v>124149514</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>56725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,16 +1678,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124149539</v>
+        <v>124149526</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -794,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149533</v>
+        <v>124149519</v>
       </c>
       <c r="B3" t="n">
-        <v>57942</v>
+        <v>57209</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,7 +841,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -918,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124169741</v>
+        <v>124149533</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57942</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1005,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149526</v>
+        <v>124149536</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>58055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1166,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124149536</v>
+        <v>124149539</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,16 +1187,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1206,11 +1211,6 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149519</v>
+        <v>124169741</v>
       </c>
       <c r="B7" t="n">
-        <v>57209</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100063</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149530</v>
+        <v>124149514</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>56725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149514</v>
+        <v>124149530</v>
       </c>
       <c r="B10" t="n">
-        <v>56725</v>
+        <v>57883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,16 +1678,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102613</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124149526</v>
+        <v>124169741</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149519</v>
+        <v>124149526</v>
       </c>
       <c r="B3" t="n">
-        <v>57209</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,33 +815,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149533</v>
+        <v>124149530</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149536</v>
+        <v>124149539</v>
       </c>
       <c r="B5" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1087,11 +1087,6 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1171,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124149539</v>
+        <v>124149536</v>
       </c>
       <c r="B6" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,16 +1182,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1211,6 +1206,11 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124169741</v>
+        <v>124149519</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57209</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149516</v>
+        <v>124149533</v>
       </c>
       <c r="B8" t="n">
-        <v>56965</v>
+        <v>57942</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149530</v>
+        <v>124149516</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>56965</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,16 +1678,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124169741</v>
+        <v>124149514</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>56725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149526</v>
+        <v>124149533</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149539</v>
+        <v>124149519</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>57209</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,34 +1059,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1290,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149519</v>
+        <v>124149539</v>
       </c>
       <c r="B7" t="n">
-        <v>57209</v>
+        <v>58191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,39 +1307,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100063</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149533</v>
+        <v>124149516</v>
       </c>
       <c r="B8" t="n">
-        <v>57942</v>
+        <v>56965</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149514</v>
+        <v>124169741</v>
       </c>
       <c r="B9" t="n">
-        <v>56725</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149516</v>
+        <v>124149526</v>
       </c>
       <c r="B10" t="n">
-        <v>56965</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,30 +1674,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149530</v>
+        <v>124149519</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57209</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,37 +935,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100063</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149519</v>
+        <v>124149530</v>
       </c>
       <c r="B5" t="n">
-        <v>57209</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,37 +1059,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100063</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124149514</v>
+        <v>124149539</v>
       </c>
       <c r="B2" t="n">
-        <v>56725</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,16 +710,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149533</v>
+        <v>124169741</v>
       </c>
       <c r="B3" t="n">
-        <v>57942</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -886,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149519</v>
+        <v>124149536</v>
       </c>
       <c r="B4" t="n">
-        <v>57209</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,37 +930,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100063</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149530</v>
+        <v>124149519</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57209</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,37 +1054,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1171,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124149536</v>
+        <v>124149514</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>56725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,16 +1182,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1206,7 +1201,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1295,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149539</v>
+        <v>124149516</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>56965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,16 +1306,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,6 +1330,11 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149516</v>
+        <v>124149530</v>
       </c>
       <c r="B8" t="n">
-        <v>56965</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124169741</v>
+        <v>124149533</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57942</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124149539</v>
+        <v>124149530</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,6 +715,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -794,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124169741</v>
+        <v>124149516</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -881,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149536</v>
+        <v>124149514</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>56725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1042,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149519</v>
+        <v>124149539</v>
       </c>
       <c r="B5" t="n">
-        <v>57209</v>
+        <v>58191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,39 +1059,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100063</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124149514</v>
+        <v>124169741</v>
       </c>
       <c r="B6" t="n">
-        <v>56725</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149516</v>
+        <v>124149526</v>
       </c>
       <c r="B7" t="n">
-        <v>56965</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,30 +1302,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149530</v>
+        <v>124149519</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57209</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,37 +1426,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100063</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149533</v>
+        <v>124149536</v>
       </c>
       <c r="B9" t="n">
-        <v>57942</v>
+        <v>58055</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,30 +1550,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149526</v>
+        <v>124149533</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,26 +1678,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124149530</v>
+        <v>124169741</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149516</v>
+        <v>124149536</v>
       </c>
       <c r="B3" t="n">
-        <v>56965</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149514</v>
+        <v>124149539</v>
       </c>
       <c r="B4" t="n">
-        <v>56725</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,16 +958,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1047,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149539</v>
+        <v>124149519</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>57209</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,34 +1054,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124169741</v>
+        <v>124149533</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57942</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149526</v>
+        <v>124149516</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,30 +1302,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149519</v>
+        <v>124149526</v>
       </c>
       <c r="B8" t="n">
-        <v>57209</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,33 +1430,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149536</v>
+        <v>124149514</v>
       </c>
       <c r="B9" t="n">
-        <v>58055</v>
+        <v>56725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149533</v>
+        <v>124149530</v>
       </c>
       <c r="B10" t="n">
-        <v>57942</v>
+        <v>57883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,30 +1674,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149536</v>
+        <v>124149539</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,11 +839,6 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -923,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149539</v>
+        <v>124149536</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,6 +958,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1784,6 +1784,122 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126215443</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57934</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kråkberget, Skidtjärn  NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>599751</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6772715</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stefan Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stefan Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>126215443</v>
       </c>
       <c r="B11" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>126215443</v>
       </c>
       <c r="B11" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>124169741</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -799,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124149539</v>
+        <v>124149519</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,30 +805,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -918,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124149536</v>
+        <v>124149514</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1042,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124149519</v>
+        <v>124149516</v>
       </c>
       <c r="B5" t="n">
-        <v>57209</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,33 +1043,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100063</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1166,15 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124149533</v>
+        <v>124149536</v>
       </c>
       <c r="B6" t="n">
-        <v>57942</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,26 +1162,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1290,42 +1270,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124149516</v>
+        <v>124149533</v>
       </c>
       <c r="B7" t="n">
-        <v>56965</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1414,15 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124149526</v>
+        <v>126215443</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,36 +1400,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kråkberget, Skidtjärn  NV, Hls</t>
@@ -1496,22 +1463,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>05:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,15 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124149514</v>
+        <v>124149530</v>
       </c>
       <c r="B9" t="n">
-        <v>56725</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,16 +1516,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1573,7 +1535,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1662,42 +1624,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124149530</v>
+        <v>124149526</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1786,32 +1743,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126215443</v>
+        <v>124149539</v>
       </c>
       <c r="B11" t="n">
-        <v>57939</v>
+        <v>58636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1819,11 +1776,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kråkberget, Skidtjärn  NV, Hls</t>
@@ -1860,22 +1815,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 14326-2024 artfynd.xlsx
+++ b/artfynd/A 14326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124169741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149519</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149514</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149516</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149536</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149533</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1502,6 +1537,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126215443</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149530</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1740,6 +1785,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149526</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1854,8 +1904,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124149539</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>